--- a/data/Att Base/_relatorio_chamados_05_06_2026, 16_07_01.xlsx
+++ b/data/Att Base/_relatorio_chamados_05_06_2026, 16_07_01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="584">
   <si>
     <t>Id</t>
   </si>
@@ -1595,6 +1595,18 @@
     <t>HPLAST EMBALAGENS FLEXIVEIS LTDA</t>
   </si>
   <si>
+    <t>Plano de Contas</t>
+  </si>
+  <si>
+    <t>Erika, bom dia!Preciso que faça a mudança no plano da DFG, atualmente está com o de clube esportivo, gostaria que mudasse para o da indústria (9011).</t>
+  </si>
+  <si>
+    <t>DFG COMERCIO IMPORTACAO, EXPORTACAO E REPRESENTACAO LTDA</t>
+  </si>
+  <si>
+    <t>vander</t>
+  </si>
+  <si>
     <t xml:space="preserve">Consulta Fiscal	Apresentada para o cliente com pendência (Sefaz). Por favor, verificar EFD 10 e 11/2025.</t>
   </si>
   <si>
@@ -1605,9 +1617,6 @@
   </si>
   <si>
     <t xml:space="preserve">NAKABOX - COMERCIO DE PECAS E ACESSORIOS PARA VEICULOS E MOTOCICLETAS LTDA  </t>
-  </si>
-  <si>
-    <t>vander</t>
   </si>
   <si>
     <t xml:space="preserve">ATITUDE / PENDENCIA	DPTO.	TIPO	AÇÃOAPRESENTADA DRE LINHA A LINHA	CONTÁBILIDADE	INFORMATIVO	 DRE APRESENTA LUCRATIVIDADE DE R$ 1.161.281,09 PORÉM FALTOU SER CONTABILIZADA DESPESA SALARIO R$ 780.595, 04 FGTS R$ 171558,71 E INSS R$ 405.011, 14 QUE MUDA SUBSTANCIALMENTE O RESULTA CONTÁBIL, POR FAVOR CORRIGIR	CONTÁBILIDADE	SOLICITAÇÃO	LANÇAR PARTE TRABALHISTADEVIDO A DIVERGÊNCIA APRESENTADA EM 01/2026, CLIENTE VAI COMPARTILHAR O CONTROLE FINANCEIRO DELE, PARA BASE DE COMPARAÇÃO COM A DRE E IDENTIICAR AS DIVERGÊNCIAS QUE IMPACTAM NO RESULTADO CONTÁBIL	CONTÁBILIDADE	INFORMATIVO	 APRESENTADA DRE LINHA A LINHA	CONTÁBILIDADE	INFORMATIVO	 </t>
@@ -1840,8 +1849,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:U274">
-  <autoFilter ref="A1:U274"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:U275">
+  <autoFilter ref="A1:U275"/>
   <tableColumns count="21">
     <tableColumn id="1" name="Id" totalsRowFunction="average"/>
     <tableColumn id="2" name="Sistema" totalsRowFunction="average"/>
@@ -1872,7 +1881,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:U274"/>
+  <dimension ref="A1:U275"/>
   <sheetFormatPr defaultRowHeight="14.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -15783,32 +15792,30 @@
     </row>
     <row r="250">
       <c r="A250" s="2">
-        <v>77018</v>
+        <v>79729</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>63</v>
+        <v>526</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>64</v>
+        <v>526</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F250" s="2">
-        <v>6520</v>
+        <v>6499</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H250" s="2"/>
-      <c r="I250" s="2" t="s">
-        <v>455</v>
-      </c>
+      <c r="I250" s="2"/>
       <c r="J250" s="2" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="K250" s="4"/>
       <c r="L250" s="4"/>
@@ -15816,29 +15823,27 @@
         <v>27</v>
       </c>
       <c r="N250" s="4">
-        <v>46057.634546875</v>
+        <v>46178.7006119213</v>
       </c>
       <c r="O250" s="4">
-        <v>46064</v>
+        <v>46218</v>
       </c>
       <c r="P250" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="Q250" s="4" t="s">
-        <v>40</v>
+        <v>529</v>
       </c>
       <c r="R250" s="4"/>
       <c r="S250" s="4"/>
       <c r="T250" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="U250" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="U250" s="2"/>
     </row>
     <row r="251">
       <c r="A251" s="2">
-        <v>79645</v>
+        <v>77018</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>63</v>
@@ -15847,21 +15852,23 @@
         <v>64</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="F251" s="2">
-        <v>6537</v>
+        <v>6520</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="H251" s="2"/>
-      <c r="I251" s="2"/>
+      <c r="I251" s="2" t="s">
+        <v>455</v>
+      </c>
       <c r="J251" s="2" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="K251" s="4"/>
       <c r="L251" s="4"/>
@@ -15869,27 +15876,29 @@
         <v>27</v>
       </c>
       <c r="N251" s="4">
-        <v>46175.7141352662</v>
+        <v>46057.634546875</v>
       </c>
       <c r="O251" s="4">
-        <v>46178</v>
+        <v>46064</v>
       </c>
       <c r="P251" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="Q251" s="4" t="s">
-        <v>530</v>
+        <v>40</v>
       </c>
       <c r="R251" s="4"/>
       <c r="S251" s="4"/>
       <c r="T251" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="U251" s="2"/>
+      <c r="U251" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2">
-        <v>78150</v>
+        <v>79645</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>63</v>
@@ -15898,23 +15907,21 @@
         <v>64</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F252" s="2">
-        <v>6559</v>
+        <v>6537</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H252" s="2"/>
-      <c r="I252" s="2" t="s">
-        <v>80</v>
-      </c>
+      <c r="I252" s="2"/>
       <c r="J252" s="2" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="K252" s="4"/>
       <c r="L252" s="4"/>
@@ -15922,54 +15929,52 @@
         <v>27</v>
       </c>
       <c r="N252" s="4">
-        <v>46105.3667060995</v>
+        <v>46175.7141352662</v>
       </c>
       <c r="O252" s="4">
-        <v>46112</v>
+        <v>46178</v>
       </c>
       <c r="P252" s="2" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="Q252" s="4" t="s">
-        <v>48</v>
+        <v>529</v>
       </c>
       <c r="R252" s="4"/>
-      <c r="S252" s="4">
-        <v>46113.6493106829</v>
-      </c>
+      <c r="S252" s="4"/>
       <c r="T252" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="U252" s="2" t="s">
-        <v>81</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="U252" s="2"/>
     </row>
     <row r="253">
       <c r="A253" s="2">
-        <v>79688</v>
+        <v>78150</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>351</v>
+        <v>63</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>351</v>
+        <v>64</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F253" s="2">
-        <v>6590</v>
+        <v>6559</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H253" s="2"/>
-      <c r="I253" s="2"/>
+      <c r="I253" s="2" t="s">
+        <v>80</v>
+      </c>
       <c r="J253" s="2" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="K253" s="4"/>
       <c r="L253" s="4"/>
@@ -15977,52 +15982,54 @@
         <v>27</v>
       </c>
       <c r="N253" s="4">
-        <v>46176.7336623843</v>
+        <v>46105.3667060995</v>
       </c>
       <c r="O253" s="4">
-        <v>46183</v>
+        <v>46112</v>
       </c>
       <c r="P253" s="2" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="Q253" s="4" t="s">
-        <v>295</v>
+        <v>48</v>
       </c>
       <c r="R253" s="4"/>
-      <c r="S253" s="4"/>
+      <c r="S253" s="4">
+        <v>46113.6493106829</v>
+      </c>
       <c r="T253" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="U253" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="U253" s="2" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2">
-        <v>78612</v>
+        <v>79688</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>63</v>
+        <v>351</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>64</v>
+        <v>351</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F254" s="2">
-        <v>6621</v>
+        <v>6590</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H254" s="2"/>
-      <c r="I254" s="2" t="s">
-        <v>47</v>
-      </c>
+      <c r="I254" s="2"/>
       <c r="J254" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="K254" s="4"/>
       <c r="L254" s="4"/>
@@ -16030,31 +16037,27 @@
         <v>27</v>
       </c>
       <c r="N254" s="4">
-        <v>46125.5933144676</v>
+        <v>46176.7336623843</v>
       </c>
       <c r="O254" s="4">
-        <v>46132</v>
+        <v>46183</v>
       </c>
       <c r="P254" s="2" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="Q254" s="4" t="s">
-        <v>93</v>
+        <v>295</v>
       </c>
       <c r="R254" s="4"/>
-      <c r="S254" s="4">
-        <v>46125.7233859954</v>
-      </c>
+      <c r="S254" s="4"/>
       <c r="T254" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="U254" s="2" t="s">
-        <v>30</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="U254" s="2"/>
     </row>
     <row r="255">
       <c r="A255" s="2">
-        <v>78613</v>
+        <v>78612</v>
       </c>
       <c r="B255" s="2" t="s">
         <v>63</v>
@@ -16066,20 +16069,20 @@
         <v>32</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F255" s="2">
         <v>6621</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="H255" s="2"/>
       <c r="I255" s="2" t="s">
-        <v>499</v>
+        <v>47</v>
       </c>
       <c r="J255" s="2" t="s">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="K255" s="4"/>
       <c r="L255" s="4"/>
@@ -16087,7 +16090,7 @@
         <v>27</v>
       </c>
       <c r="N255" s="4">
-        <v>46125.5936851852</v>
+        <v>46125.5933144676</v>
       </c>
       <c r="O255" s="4">
         <v>46132</v>
@@ -16100,18 +16103,18 @@
       </c>
       <c r="R255" s="4"/>
       <c r="S255" s="4">
-        <v>46175.5689032407</v>
+        <v>46125.7233859954</v>
       </c>
       <c r="T255" s="2" t="s">
-        <v>499</v>
+        <v>47</v>
       </c>
       <c r="U255" s="2" t="s">
-        <v>538</v>
+        <v>30</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2">
-        <v>78614</v>
+        <v>78613</v>
       </c>
       <c r="B256" s="2" t="s">
         <v>63</v>
@@ -16123,20 +16126,20 @@
         <v>32</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F256" s="2">
         <v>6621</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="H256" s="2"/>
       <c r="I256" s="2" t="s">
-        <v>189</v>
+        <v>499</v>
       </c>
       <c r="J256" s="2" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="K256" s="4"/>
       <c r="L256" s="4"/>
@@ -16144,29 +16147,31 @@
         <v>27</v>
       </c>
       <c r="N256" s="4">
-        <v>46125.594015162</v>
+        <v>46125.5936851852</v>
       </c>
       <c r="O256" s="4">
         <v>46132</v>
       </c>
       <c r="P256" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="Q256" s="4" t="s">
         <v>93</v>
       </c>
       <c r="R256" s="4"/>
-      <c r="S256" s="4"/>
+      <c r="S256" s="4">
+        <v>46175.5689032407</v>
+      </c>
       <c r="T256" s="2" t="s">
-        <v>27</v>
+        <v>499</v>
       </c>
       <c r="U256" s="2" t="s">
-        <v>27</v>
+        <v>541</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2">
-        <v>78615</v>
+        <v>78614</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>63</v>
@@ -16178,13 +16183,13 @@
         <v>32</v>
       </c>
       <c r="E257" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="F257" s="2">
+        <v>6621</v>
+      </c>
+      <c r="G257" s="2" t="s">
         <v>539</v>
-      </c>
-      <c r="F257" s="2">
-        <v>6622</v>
-      </c>
-      <c r="G257" s="2" t="s">
-        <v>540</v>
       </c>
       <c r="H257" s="2"/>
       <c r="I257" s="2" t="s">
@@ -16199,7 +16204,7 @@
         <v>27</v>
       </c>
       <c r="N257" s="4">
-        <v>46125.5944423264</v>
+        <v>46125.594015162</v>
       </c>
       <c r="O257" s="4">
         <v>46132</v>
@@ -16221,7 +16226,7 @@
     </row>
     <row r="258">
       <c r="A258" s="2">
-        <v>76937</v>
+        <v>78615</v>
       </c>
       <c r="B258" s="2" t="s">
         <v>63</v>
@@ -16233,17 +16238,17 @@
         <v>32</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F258" s="2">
-        <v>6638</v>
+        <v>6622</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H258" s="2"/>
       <c r="I258" s="2" t="s">
-        <v>469</v>
+        <v>189</v>
       </c>
       <c r="J258" s="2" t="s">
         <v>43</v>
@@ -16254,16 +16259,16 @@
         <v>27</v>
       </c>
       <c r="N258" s="4">
-        <v>46055.4564325231</v>
+        <v>46125.5944423264</v>
       </c>
       <c r="O258" s="4">
-        <v>46062</v>
+        <v>46132</v>
       </c>
       <c r="P258" s="2" t="s">
         <v>36</v>
       </c>
       <c r="Q258" s="4" t="s">
-        <v>29</v>
+        <v>93</v>
       </c>
       <c r="R258" s="4"/>
       <c r="S258" s="4"/>
@@ -16276,7 +16281,7 @@
     </row>
     <row r="259">
       <c r="A259" s="2">
-        <v>77639</v>
+        <v>76937</v>
       </c>
       <c r="B259" s="2" t="s">
         <v>63</v>
@@ -16288,13 +16293,13 @@
         <v>32</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F259" s="2">
-        <v>6640</v>
+        <v>6638</v>
       </c>
       <c r="G259" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H259" s="2"/>
       <c r="I259" s="2" t="s">
@@ -16309,10 +16314,10 @@
         <v>27</v>
       </c>
       <c r="N259" s="4">
-        <v>46083.6026024306</v>
+        <v>46055.4564325231</v>
       </c>
       <c r="O259" s="4">
-        <v>46086</v>
+        <v>46062</v>
       </c>
       <c r="P259" s="2" t="s">
         <v>36</v>
@@ -16331,30 +16336,32 @@
     </row>
     <row r="260">
       <c r="A260" s="2">
-        <v>79669</v>
+        <v>77639</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>351</v>
+        <v>63</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>351</v>
+        <v>64</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F260" s="2">
-        <v>6880</v>
+        <v>6640</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H260" s="2"/>
-      <c r="I260" s="2"/>
+      <c r="I260" s="2" t="s">
+        <v>469</v>
+      </c>
       <c r="J260" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K260" s="4"/>
       <c r="L260" s="4"/>
@@ -16362,50 +16369,52 @@
         <v>27</v>
       </c>
       <c r="N260" s="4">
-        <v>46176.5097496528</v>
+        <v>46083.6026024306</v>
       </c>
       <c r="O260" s="4">
-        <v>46178</v>
+        <v>46086</v>
       </c>
       <c r="P260" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="Q260" s="4" t="s">
-        <v>145</v>
+        <v>29</v>
       </c>
       <c r="R260" s="4"/>
       <c r="S260" s="4"/>
       <c r="T260" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="U260" s="2"/>
+      <c r="U260" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2">
-        <v>78847</v>
+        <v>79669</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>21</v>
+        <v>351</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>64</v>
+        <v>351</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F261" s="2">
-        <v>0</v>
-      </c>
-      <c r="G261" s="2"/>
+        <v>6880</v>
+      </c>
+      <c r="G261" s="2" t="s">
+        <v>549</v>
+      </c>
       <c r="H261" s="2"/>
-      <c r="I261" s="2" t="s">
-        <v>548</v>
-      </c>
+      <c r="I261" s="2"/>
       <c r="J261" s="2" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="K261" s="4"/>
       <c r="L261" s="4"/>
@@ -16413,36 +16422,30 @@
         <v>27</v>
       </c>
       <c r="N261" s="4">
-        <v>46134.6696519329</v>
+        <v>46176.5097496528</v>
       </c>
       <c r="O261" s="4">
-        <v>46142</v>
+        <v>46178</v>
       </c>
       <c r="P261" s="2" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="Q261" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="R261" s="4">
-        <v>46171.5943925926</v>
-      </c>
-      <c r="S261" s="4">
-        <v>46176.7635253819</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="R261" s="4"/>
+      <c r="S261" s="4"/>
       <c r="T261" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="U261" s="2" t="s">
-        <v>549</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="U261" s="2"/>
     </row>
     <row r="262">
       <c r="A262" s="2">
-        <v>78425</v>
+        <v>78847</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="C262" s="2" t="s">
         <v>64</v>
@@ -16454,17 +16457,15 @@
         <v>550</v>
       </c>
       <c r="F262" s="2">
-        <v>1180</v>
-      </c>
-      <c r="G262" s="2" t="s">
-        <v>551</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G262" s="2"/>
       <c r="H262" s="2"/>
       <c r="I262" s="2" t="s">
-        <v>25</v>
+        <v>551</v>
       </c>
       <c r="J262" s="2" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="K262" s="4"/>
       <c r="L262" s="4"/>
@@ -16472,10 +16473,10 @@
         <v>27</v>
       </c>
       <c r="N262" s="4">
-        <v>46113.6894368403</v>
+        <v>46134.6696519329</v>
       </c>
       <c r="O262" s="4">
-        <v>46120</v>
+        <v>46142</v>
       </c>
       <c r="P262" s="2" t="s">
         <v>28</v>
@@ -16483,20 +16484,22 @@
       <c r="Q262" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="R262" s="4"/>
+      <c r="R262" s="4">
+        <v>46171.5943925926</v>
+      </c>
       <c r="S262" s="4">
-        <v>46114.6203158912</v>
+        <v>46176.7635253819</v>
       </c>
       <c r="T262" s="2" t="s">
-        <v>25</v>
+        <v>551</v>
       </c>
       <c r="U262" s="2" t="s">
-        <v>30</v>
+        <v>552</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2">
-        <v>78854</v>
+        <v>78425</v>
       </c>
       <c r="B263" s="2" t="s">
         <v>63</v>
@@ -16508,20 +16511,20 @@
         <v>32</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F263" s="2">
-        <v>4811</v>
+        <v>1180</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>272</v>
+        <v>554</v>
       </c>
       <c r="H263" s="2"/>
       <c r="I263" s="2" t="s">
-        <v>520</v>
+        <v>25</v>
       </c>
       <c r="J263" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="K263" s="4"/>
       <c r="L263" s="4"/>
@@ -16529,29 +16532,31 @@
         <v>27</v>
       </c>
       <c r="N263" s="4">
-        <v>46134.7473862616</v>
+        <v>46113.6894368403</v>
       </c>
       <c r="O263" s="4">
-        <v>46142</v>
+        <v>46120</v>
       </c>
       <c r="P263" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="Q263" s="4" t="s">
         <v>93</v>
       </c>
       <c r="R263" s="4"/>
-      <c r="S263" s="4"/>
+      <c r="S263" s="4">
+        <v>46114.6203158912</v>
+      </c>
       <c r="T263" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="U263" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2">
-        <v>78445</v>
+        <v>78854</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>63</v>
@@ -16563,17 +16568,17 @@
         <v>32</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="F264" s="2">
-        <v>5100</v>
+        <v>4811</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>302</v>
+        <v>272</v>
       </c>
       <c r="H264" s="2"/>
       <c r="I264" s="2" t="s">
-        <v>486</v>
+        <v>520</v>
       </c>
       <c r="J264" s="2" t="s">
         <v>43</v>
@@ -16584,10 +16589,10 @@
         <v>27</v>
       </c>
       <c r="N264" s="4">
-        <v>46114.5757072917</v>
+        <v>46134.7473862616</v>
       </c>
       <c r="O264" s="4">
-        <v>46121</v>
+        <v>46142</v>
       </c>
       <c r="P264" s="2" t="s">
         <v>36</v>
@@ -16606,19 +16611,19 @@
     </row>
     <row r="265">
       <c r="A265" s="2">
-        <v>78446</v>
+        <v>78445</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="D265" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="F265" s="2">
         <v>5100</v>
@@ -16628,10 +16633,10 @@
       </c>
       <c r="H265" s="2"/>
       <c r="I265" s="2" t="s">
-        <v>25</v>
+        <v>486</v>
       </c>
       <c r="J265" s="2" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="K265" s="4"/>
       <c r="L265" s="4"/>
@@ -16639,37 +16644,35 @@
         <v>27</v>
       </c>
       <c r="N265" s="4">
-        <v>46114.5766481134</v>
+        <v>46114.5757072917</v>
       </c>
       <c r="O265" s="4">
         <v>46121</v>
       </c>
       <c r="P265" s="2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q265" s="4" t="s">
         <v>93</v>
       </c>
       <c r="R265" s="4"/>
-      <c r="S265" s="4">
-        <v>46114.6198500347</v>
-      </c>
+      <c r="S265" s="4"/>
       <c r="T265" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="U265" s="2" t="s">
-        <v>555</v>
+        <v>27</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2">
-        <v>79640</v>
+        <v>78446</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>556</v>
+        <v>21</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>556</v>
+        <v>22</v>
       </c>
       <c r="D266" s="3" t="s">
         <v>32</v>
@@ -16678,17 +16681,17 @@
         <v>557</v>
       </c>
       <c r="F266" s="2">
-        <v>5726</v>
+        <v>5100</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>558</v>
+        <v>302</v>
       </c>
       <c r="H266" s="2"/>
       <c r="I266" s="2" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="J266" s="2" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="K266" s="4"/>
       <c r="L266" s="4"/>
@@ -16696,54 +16699,56 @@
         <v>27</v>
       </c>
       <c r="N266" s="4">
-        <v>46175.7045628125</v>
+        <v>46114.5766481134</v>
       </c>
       <c r="O266" s="4">
-        <v>46178</v>
+        <v>46121</v>
       </c>
       <c r="P266" s="2" t="s">
         <v>28</v>
       </c>
       <c r="Q266" s="4" t="s">
-        <v>559</v>
+        <v>93</v>
       </c>
       <c r="R266" s="4"/>
       <c r="S266" s="4">
-        <v>46178.4519851852</v>
+        <v>46114.6198500347</v>
       </c>
       <c r="T266" s="2" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="U266" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2">
-        <v>79641</v>
+        <v>79640</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="D267" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F267" s="2">
         <v>5726</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="H267" s="2"/>
-      <c r="I267" s="2"/>
+      <c r="I267" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="J267" s="2" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="K267" s="4"/>
       <c r="L267" s="4"/>
@@ -16751,52 +16756,54 @@
         <v>27</v>
       </c>
       <c r="N267" s="4">
-        <v>46175.7050956829</v>
+        <v>46175.7045628125</v>
       </c>
       <c r="O267" s="4">
         <v>46178</v>
       </c>
       <c r="P267" s="2" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="Q267" s="4" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="R267" s="4"/>
-      <c r="S267" s="4"/>
+      <c r="S267" s="4">
+        <v>46178.4519851852</v>
+      </c>
       <c r="T267" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="U267" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="U267" s="2" t="s">
+        <v>563</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2">
-        <v>78447</v>
+        <v>79641</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>63</v>
+        <v>559</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>64</v>
+        <v>559</v>
       </c>
       <c r="D268" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="F268" s="2">
-        <v>5740</v>
+        <v>5726</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H268" s="2"/>
-      <c r="I268" s="2" t="s">
-        <v>189</v>
-      </c>
+      <c r="I268" s="2"/>
       <c r="J268" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K268" s="4"/>
       <c r="L268" s="4"/>
@@ -16804,54 +16811,52 @@
         <v>27</v>
       </c>
       <c r="N268" s="4">
-        <v>46114.5825532755</v>
+        <v>46175.7050956829</v>
       </c>
       <c r="O268" s="4">
-        <v>46121</v>
+        <v>46178</v>
       </c>
       <c r="P268" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="Q268" s="4" t="s">
-        <v>93</v>
+        <v>562</v>
       </c>
       <c r="R268" s="4"/>
       <c r="S268" s="4"/>
       <c r="T268" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="U268" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="U268" s="2"/>
     </row>
     <row r="269">
       <c r="A269" s="2">
-        <v>79569</v>
+        <v>78447</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>126</v>
+        <v>64</v>
       </c>
       <c r="D269" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F269" s="2">
-        <v>5909</v>
+        <v>5740</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>410</v>
+        <v>566</v>
       </c>
       <c r="H269" s="2"/>
       <c r="I269" s="2" t="s">
-        <v>565</v>
+        <v>189</v>
       </c>
       <c r="J269" s="2" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="K269" s="4"/>
       <c r="L269" s="4"/>
@@ -16859,54 +16864,54 @@
         <v>27</v>
       </c>
       <c r="N269" s="4">
-        <v>46174.4588620718</v>
+        <v>46114.5825532755</v>
       </c>
       <c r="O269" s="4">
-        <v>46176</v>
+        <v>46121</v>
       </c>
       <c r="P269" s="2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q269" s="4" t="s">
-        <v>559</v>
+        <v>93</v>
       </c>
       <c r="R269" s="4"/>
-      <c r="S269" s="4">
-        <v>46178.363075081</v>
-      </c>
+      <c r="S269" s="4"/>
       <c r="T269" s="2" t="s">
-        <v>565</v>
+        <v>27</v>
       </c>
       <c r="U269" s="2" t="s">
-        <v>566</v>
+        <v>27</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2">
-        <v>77046</v>
+        <v>79569</v>
       </c>
       <c r="B270" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D270" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E270" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="C270" s="2" t="s">
+      <c r="F270" s="2">
+        <v>5909</v>
+      </c>
+      <c r="G270" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="H270" s="2"/>
+      <c r="I270" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="D270" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="E270" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="F270" s="2">
-        <v>6422</v>
-      </c>
-      <c r="G270" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="H270" s="2"/>
-      <c r="I270" s="2"/>
       <c r="J270" s="2" t="s">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="K270" s="4"/>
       <c r="L270" s="4"/>
@@ -16914,52 +16919,54 @@
         <v>27</v>
       </c>
       <c r="N270" s="4">
-        <v>46059.6455982986</v>
+        <v>46174.4588620718</v>
       </c>
       <c r="O270" s="4">
-        <v>46064</v>
+        <v>46176</v>
       </c>
       <c r="P270" s="2" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="Q270" s="4" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="R270" s="4"/>
-      <c r="S270" s="4"/>
+      <c r="S270" s="4">
+        <v>46178.363075081</v>
+      </c>
       <c r="T270" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="U270" s="2"/>
+        <v>568</v>
+      </c>
+      <c r="U270" s="2" t="s">
+        <v>569</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2">
-        <v>79689</v>
+        <v>77046</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>63</v>
+        <v>570</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>64</v>
+        <v>571</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>32</v>
+        <v>572</v>
       </c>
       <c r="E271" s="2" t="s">
         <v>573</v>
       </c>
       <c r="F271" s="2">
-        <v>6427</v>
+        <v>6422</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>513</v>
+        <v>574</v>
       </c>
       <c r="H271" s="2"/>
-      <c r="I271" s="2" t="s">
-        <v>385</v>
-      </c>
+      <c r="I271" s="2"/>
       <c r="J271" s="2" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="K271" s="4"/>
       <c r="L271" s="4"/>
@@ -16967,33 +16974,27 @@
         <v>27</v>
       </c>
       <c r="N271" s="4">
-        <v>46176.7359756597</v>
+        <v>46059.6455982986</v>
       </c>
       <c r="O271" s="4">
-        <v>46181</v>
+        <v>46064</v>
       </c>
       <c r="P271" s="2" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="Q271" s="4" t="s">
-        <v>559</v>
-      </c>
-      <c r="R271" s="4">
-        <v>46178.6529883102</v>
-      </c>
-      <c r="S271" s="4">
-        <v>46178.6534081829</v>
-      </c>
+        <v>575</v>
+      </c>
+      <c r="R271" s="4"/>
+      <c r="S271" s="4"/>
       <c r="T271" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="U271" s="2" t="s">
-        <v>574</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="U271" s="2"/>
     </row>
     <row r="272">
       <c r="A272" s="2">
-        <v>79691</v>
+        <v>79689</v>
       </c>
       <c r="B272" s="2" t="s">
         <v>63</v>
@@ -17005,7 +17006,7 @@
         <v>32</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F272" s="2">
         <v>6427</v>
@@ -17026,7 +17027,7 @@
         <v>27</v>
       </c>
       <c r="N272" s="4">
-        <v>46176.7397660069</v>
+        <v>46176.7359756597</v>
       </c>
       <c r="O272" s="4">
         <v>46181</v>
@@ -17035,22 +17036,24 @@
         <v>28</v>
       </c>
       <c r="Q272" s="4" t="s">
-        <v>559</v>
-      </c>
-      <c r="R272" s="4"/>
+        <v>562</v>
+      </c>
+      <c r="R272" s="4">
+        <v>46178.6529883102</v>
+      </c>
       <c r="S272" s="4">
-        <v>46178.6505528588</v>
+        <v>46178.6534081829</v>
       </c>
       <c r="T272" s="2" t="s">
         <v>385</v>
       </c>
       <c r="U272" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2">
-        <v>79692</v>
+        <v>79691</v>
       </c>
       <c r="B273" s="2" t="s">
         <v>63</v>
@@ -17062,7 +17065,7 @@
         <v>32</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F273" s="2">
         <v>6427</v>
@@ -17083,7 +17086,7 @@
         <v>27</v>
       </c>
       <c r="N273" s="4">
-        <v>46176.7448095255</v>
+        <v>46176.7397660069</v>
       </c>
       <c r="O273" s="4">
         <v>46181</v>
@@ -17092,22 +17095,22 @@
         <v>28</v>
       </c>
       <c r="Q273" s="4" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="R273" s="4"/>
       <c r="S273" s="4">
-        <v>46178.6507270833</v>
+        <v>46178.6505528588</v>
       </c>
       <c r="T273" s="2" t="s">
         <v>385</v>
       </c>
       <c r="U273" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2">
-        <v>79115</v>
+        <v>79692</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>63</v>
@@ -17119,20 +17122,20 @@
         <v>32</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="F274" s="2">
-        <v>9578</v>
+        <v>6427</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>579</v>
+        <v>513</v>
       </c>
       <c r="H274" s="2"/>
       <c r="I274" s="2" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="J274" s="2" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="K274" s="4"/>
       <c r="L274" s="4"/>
@@ -17140,26 +17143,83 @@
         <v>27</v>
       </c>
       <c r="N274" s="4">
-        <v>46153.5882722222</v>
+        <v>46176.7448095255</v>
       </c>
       <c r="O274" s="4">
-        <v>46160</v>
+        <v>46181</v>
       </c>
       <c r="P274" s="2" t="s">
         <v>28</v>
       </c>
       <c r="Q274" s="4" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="R274" s="4"/>
       <c r="S274" s="4">
+        <v>46178.6507270833</v>
+      </c>
+      <c r="T274" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="U274" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2">
+        <v>79115</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C275" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D275" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="F275" s="2">
+        <v>9578</v>
+      </c>
+      <c r="G275" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="H275" s="2"/>
+      <c r="I275" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="J275" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K275" s="4"/>
+      <c r="L275" s="4"/>
+      <c r="M275" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N275" s="4">
+        <v>46153.5882722222</v>
+      </c>
+      <c r="O275" s="4">
+        <v>46160</v>
+      </c>
+      <c r="P275" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q275" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="R275" s="4"/>
+      <c r="S275" s="4">
         <v>46178.6032187847</v>
       </c>
-      <c r="T274" s="2" t="s">
+      <c r="T275" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="U274" s="2" t="s">
-        <v>580</v>
+      <c r="U275" s="2" t="s">
+        <v>583</v>
       </c>
     </row>
   </sheetData>
